--- a/task191/golden/augment_decision_2027Q1.xlsx
+++ b/task191/golden/augment_decision_2027Q1.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="44">
   <si>
     <t>Stroomhuis: interconnect augment decision, first quarter 2027</t>
   </si>
@@ -36,13 +36,13 @@
     <t>Comes closest</t>
   </si>
   <si>
-    <t>HVT-01, 412 kbps</t>
-  </si>
-  <si>
-    <t>The call would change at</t>
-  </si>
-  <si>
-    <t>489 kbps</t>
+    <t>HVT-01, 318 kbps</t>
+  </si>
+  <si>
+    <t>Evenings left out</t>
+  </si>
+  <si>
+    <t>14, on which work was booked inside an evening window</t>
   </si>
   <si>
     <t>Interconnect</t>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>2027-02-25</t>
+  </si>
+  <si>
+    <t>2027-03-21</t>
   </si>
   <si>
     <t>2027-01-21</t>
@@ -595,7 +598,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="7">
-        <v>301</v>
+        <v>246</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>14</v>
@@ -609,7 +612,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="7">
-        <v>371</v>
+        <v>303</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>16</v>
@@ -623,7 +626,7 @@
         <v>17</v>
       </c>
       <c r="C11" s="7">
-        <v>298</v>
+        <v>250</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>18</v>
@@ -637,7 +640,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="7">
-        <v>412</v>
+        <v>318</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>20</v>
@@ -651,7 +654,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="7">
-        <v>311</v>
+        <v>248</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>21</v>
@@ -665,7 +668,7 @@
         <v>17</v>
       </c>
       <c r="C14" s="7">
-        <v>345</v>
+        <v>269</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>22</v>
@@ -679,7 +682,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="7">
-        <v>368</v>
+        <v>285</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>24</v>
@@ -693,7 +696,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="7">
-        <v>350</v>
+        <v>278</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>25</v>
@@ -707,7 +710,7 @@
         <v>17</v>
       </c>
       <c r="C17" s="7">
-        <v>306</v>
+        <v>247</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>26</v>
@@ -721,7 +724,7 @@
         <v>13</v>
       </c>
       <c r="C18" s="7">
-        <v>397</v>
+        <v>311</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>28</v>
@@ -735,10 +738,10 @@
         <v>15</v>
       </c>
       <c r="C19" s="7">
-        <v>334</v>
+        <v>268</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -749,105 +752,105 @@
         <v>17</v>
       </c>
       <c r="C20" s="7">
-        <v>380</v>
+        <v>301</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C21" s="7">
-        <v>332</v>
+        <v>263</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="7">
-        <v>385</v>
+        <v>307</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="7">
-        <v>392</v>
+        <v>306</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C24" s="7">
-        <v>370</v>
+        <v>290</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="7">
-        <v>333</v>
+        <v>265</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="7">
-        <v>400</v>
+        <v>312</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C27" s="7">
-        <v>311</v>
+        <v>249</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>16</v>
@@ -855,40 +858,40 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="7">
-        <v>296</v>
+        <v>241</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C29" s="7">
-        <v>291</v>
+        <v>237</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
